--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/SOUTH_CAROLINA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/SOUTH_CAROLINA_2016.xlsx
@@ -733,7 +733,7 @@
         <v>9</v>
       </c>
       <c r="D21">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="22">
@@ -3883,7 +3883,7 @@
         <v>9</v>
       </c>
       <c r="D196">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="197">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C245">
@@ -6061,7 +6061,7 @@
         <v>9</v>
       </c>
       <c r="D317">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="318">
@@ -6511,7 +6511,7 @@
         <v>9</v>
       </c>
       <c r="D342">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="343">
@@ -11425,7 +11425,7 @@
         <v>9</v>
       </c>
       <c r="D615">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="616">
@@ -11857,7 +11857,7 @@
         <v>9</v>
       </c>
       <c r="D639">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="640">
@@ -11965,7 +11965,7 @@
         <v>9</v>
       </c>
       <c r="D645">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="646">
@@ -12210,14 +12210,14 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C659">
         <v>9</v>
       </c>
       <c r="D659">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="660">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 26-</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C660">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C686">
@@ -12919,7 +12919,7 @@
         <v>9</v>
       </c>
       <c r="D698">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="699">
@@ -13099,7 +13099,7 @@
         <v>9</v>
       </c>
       <c r="D708">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="709">
@@ -13711,7 +13711,7 @@
         <v>9</v>
       </c>
       <c r="D742">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="743">
@@ -14089,7 +14089,7 @@
         <v>9</v>
       </c>
       <c r="D763">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="764">
@@ -14665,7 +14665,7 @@
         <v>9</v>
       </c>
       <c r="D795">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="796">
@@ -14719,7 +14719,7 @@
         <v>9</v>
       </c>
       <c r="D798">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="799">
@@ -14899,7 +14899,7 @@
         <v>9</v>
       </c>
       <c r="D808">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="809">
@@ -15961,7 +15961,7 @@
         <v>9</v>
       </c>
       <c r="D867">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="868">
@@ -16159,7 +16159,7 @@
         <v>9</v>
       </c>
       <c r="D878">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="879">
@@ -16573,7 +16573,7 @@
         <v>9</v>
       </c>
       <c r="D901">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="902">
@@ -16663,7 +16663,7 @@
         <v>9</v>
       </c>
       <c r="D906">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="907">
@@ -18013,7 +18013,7 @@
         <v>9</v>
       </c>
       <c r="D981">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="982">
@@ -19021,7 +19021,7 @@
         <v>9</v>
       </c>
       <c r="D1037">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="1038">
@@ -19039,7 +19039,7 @@
         <v>9</v>
       </c>
       <c r="D1038">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="1039">
@@ -19543,7 +19543,7 @@
         <v>9</v>
       </c>
       <c r="D1066">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="1067">
@@ -19669,7 +19669,7 @@
         <v>9</v>
       </c>
       <c r="D1073">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="1074">
@@ -20461,7 +20461,7 @@
         <v>9</v>
       </c>
       <c r="D1117">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="1118">
@@ -20857,7 +20857,7 @@
         <v>9</v>
       </c>
       <c r="D1139">
-        <v>0.0009068923821039903</v>
+        <v>0.0009068923821039904</v>
       </c>
     </row>
     <row r="1140">
